--- a/L-shaped/Final_codes/data/production_capacity_scenarios.xlsx
+++ b/L-shaped/Final_codes/data/production_capacity_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B623EADA-1419-4F28-BEA5-F007C3AA68FA}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A267952-652E-4DD8-BBDE-F95BB21A6EA1}"/>
   <bookViews>
     <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,20 @@
     <sheet name="supply_chain" sheetId="11" r:id="rId6"/>
     <sheet name="other" sheetId="13" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3859,6 +3872,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/L-shaped/Final_codes/data/production_capacity_scenarios.xlsx
+++ b/L-shaped/Final_codes/data/production_capacity_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A267952-652E-4DD8-BBDE-F95BB21A6EA1}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54345EC6-37B5-4AA4-9114-DF12A2F548A0}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -163,6 +163,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,6 +456,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
